--- a/dataset_t6_grouped/results2/G2/G2_T0860_W0027F0003T0006Z000C1N27_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G2/G2_T0860_W0027F0003T0006Z000C1N27_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>79.85668082831403</v>
+        <v>12.97671063460103</v>
       </c>
       <c r="D2" t="n">
-        <v>80.61169741410066</v>
+        <v>13.09940082979136</v>
       </c>
       <c r="E2" t="n">
-        <v>20.3232042025302</v>
+        <v>3.302520682911157</v>
       </c>
       <c r="F2" t="n">
-        <v>20.04158342688307</v>
+        <v>3.256757306868499</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>42.49529252592876</v>
+        <v>6.905485035463424</v>
       </c>
       <c r="D3" t="n">
-        <v>43.20594636121049</v>
+        <v>7.020966283696706</v>
       </c>
       <c r="E3" t="n">
-        <v>20.3232042025302</v>
+        <v>3.302520682911157</v>
       </c>
       <c r="F3" t="n">
-        <v>20.04158342688307</v>
+        <v>3.256757306868499</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>61.02939133901489</v>
+        <v>9.917276092589919</v>
       </c>
       <c r="D4" t="n">
-        <v>60.68636461445383</v>
+        <v>9.861534249848747</v>
       </c>
       <c r="E4" t="n">
-        <v>20.3232042025302</v>
+        <v>3.302520682911157</v>
       </c>
       <c r="F4" t="n">
-        <v>20.04158342688307</v>
+        <v>3.256757306868499</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>50.44886806366984</v>
+        <v>8.19794106034635</v>
       </c>
       <c r="D5" t="n">
-        <v>50.39266164212823</v>
+        <v>8.188807516845838</v>
       </c>
       <c r="E5" t="n">
-        <v>20.3232042025302</v>
+        <v>3.302520682911157</v>
       </c>
       <c r="F5" t="n">
-        <v>20.04158342688307</v>
+        <v>3.256757306868499</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>59.61148021244267</v>
+        <v>9.686865534521935</v>
       </c>
       <c r="D6" t="n">
-        <v>60.8042810645261</v>
+        <v>9.880695672985492</v>
       </c>
       <c r="E6" t="n">
-        <v>20.3232042025302</v>
+        <v>3.302520682911157</v>
       </c>
       <c r="F6" t="n">
-        <v>20.04158342688307</v>
+        <v>3.256757306868499</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>49.73214001882918</v>
+        <v>8.081472753059742</v>
       </c>
       <c r="D7" t="n">
-        <v>49.10577952114868</v>
+        <v>7.97968917218666</v>
       </c>
       <c r="E7" t="n">
-        <v>20.3232042025302</v>
+        <v>3.302520682911157</v>
       </c>
       <c r="F7" t="n">
-        <v>20.04158342688307</v>
+        <v>3.256757306868499</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>2.543177915917289</v>
+        <v>0.4132664113365594</v>
       </c>
       <c r="D8" t="n">
-        <v>3.686105263333523</v>
+        <v>0.5989921052916974</v>
       </c>
       <c r="E8" t="n">
-        <v>20.3232042025302</v>
+        <v>3.302520682911157</v>
       </c>
       <c r="F8" t="n">
-        <v>20.04158342688307</v>
+        <v>3.256757306868499</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>27.90909430493005</v>
+        <v>4.535227824551134</v>
       </c>
       <c r="D9" t="n">
-        <v>28.75755628699563</v>
+        <v>4.67310289663679</v>
       </c>
       <c r="E9" t="n">
-        <v>20.3232042025302</v>
+        <v>3.302520682911157</v>
       </c>
       <c r="F9" t="n">
-        <v>20.04158342688307</v>
+        <v>3.256757306868499</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>55.3781447928087</v>
+        <v>8.998948528831413</v>
       </c>
       <c r="D10" t="n">
-        <v>55.98982370180716</v>
+        <v>9.098346351543665</v>
       </c>
       <c r="E10" t="n">
-        <v>20.3232042025302</v>
+        <v>3.302520682911157</v>
       </c>
       <c r="F10" t="n">
-        <v>20.04158342688307</v>
+        <v>3.256757306868499</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>64.27304925404334</v>
+        <v>10.44437050378204</v>
       </c>
       <c r="D11" t="n">
-        <v>63.06892435340294</v>
+        <v>10.24870020742798</v>
       </c>
       <c r="E11" t="n">
-        <v>20.3232042025302</v>
+        <v>3.302520682911157</v>
       </c>
       <c r="F11" t="n">
-        <v>20.04158342688307</v>
+        <v>3.256757306868499</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
